--- a/uploads/Max_3.xlsx
+++ b/uploads/Max_3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\NEW SYSTEM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B90232C7-3522-4DFB-A058-811BA2AB990B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EAB4327-E2C0-4D29-BB95-3BDB2DC1CE9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="16200" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16935" yWindow="2100" windowWidth="11535" windowHeight="12810" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EUR " sheetId="11" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="22">
   <si>
     <t>Date</t>
   </si>
@@ -90,6 +90,9 @@
   </si>
   <si>
     <t>31/3/2026</t>
+  </si>
+  <si>
+    <t> 2026-04-14</t>
   </si>
 </sst>
 </file>
@@ -216,7 +219,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -272,6 +275,10 @@
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -14425,7 +14432,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC0DCE6A-E542-4A83-ACFA-B4956F29450C}">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" style="16" customWidth="1"/>
@@ -14471,7 +14478,7 @@
         <v>162331</v>
       </c>
       <c r="D2" s="11">
-        <f t="shared" ref="D2:D22" si="0">B2-C2</f>
+        <f t="shared" ref="D2:D26" si="0">B2-C2</f>
         <v>73589</v>
       </c>
       <c r="E2" s="1">
@@ -14481,7 +14488,7 @@
         <v>1584</v>
       </c>
       <c r="G2" s="1">
-        <f t="shared" ref="G2:G22" si="1">E2-F2</f>
+        <f t="shared" ref="G2:G26" si="1">E2-F2</f>
         <v>-18206</v>
       </c>
     </row>
@@ -14983,6 +14990,106 @@
       <c r="G22" s="22">
         <f t="shared" si="1"/>
         <v>-8772</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="26">
+        <v>46119</v>
+      </c>
+      <c r="B23" s="7">
+        <v>200946</v>
+      </c>
+      <c r="C23" s="7">
+        <v>208487</v>
+      </c>
+      <c r="D23" s="2">
+        <f t="shared" si="0"/>
+        <v>-7541</v>
+      </c>
+      <c r="E23">
+        <v>778</v>
+      </c>
+      <c r="F23" s="7">
+        <v>8826</v>
+      </c>
+      <c r="G23" s="22">
+        <f t="shared" si="1"/>
+        <v>-8048</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="30">
+        <v>46126</v>
+      </c>
+      <c r="B24" s="7">
+        <v>129517</v>
+      </c>
+      <c r="C24" s="7">
+        <v>64442</v>
+      </c>
+      <c r="D24" s="2">
+        <f t="shared" si="0"/>
+        <v>65075</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-8442</v>
+      </c>
+      <c r="F24" s="7">
+        <v>-2704</v>
+      </c>
+      <c r="G24" s="22">
+        <f t="shared" si="1"/>
+        <v>-5738</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="26">
+        <v>46126</v>
+      </c>
+      <c r="B25" s="7">
+        <v>214639</v>
+      </c>
+      <c r="C25" s="7">
+        <v>188621</v>
+      </c>
+      <c r="D25" s="2">
+        <f t="shared" si="0"/>
+        <v>26018</v>
+      </c>
+      <c r="E25" s="7">
+        <v>13693</v>
+      </c>
+      <c r="F25" s="7">
+        <v>-19866</v>
+      </c>
+      <c r="G25" s="22">
+        <f t="shared" si="1"/>
+        <v>33559</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="26">
+        <v>46133</v>
+      </c>
+      <c r="B26" s="7">
+        <v>217407</v>
+      </c>
+      <c r="C26" s="7">
+        <v>176083</v>
+      </c>
+      <c r="D26" s="2">
+        <f t="shared" si="0"/>
+        <v>41324</v>
+      </c>
+      <c r="E26" s="7">
+        <v>2768</v>
+      </c>
+      <c r="F26" s="7">
+        <v>-12538</v>
+      </c>
+      <c r="G26" s="22">
+        <f t="shared" si="1"/>
+        <v>15306</v>
       </c>
     </row>
   </sheetData>
@@ -14994,7 +15101,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E049AD9-8C60-4A1C-9327-32192CC888AD}">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" style="16" customWidth="1"/>
@@ -15040,7 +15147,7 @@
         <v>31631</v>
       </c>
       <c r="D2" s="11">
-        <f t="shared" ref="D2:D22" si="0">B2-C2</f>
+        <f t="shared" ref="D2:D25" si="0">B2-C2</f>
         <v>-15627</v>
       </c>
       <c r="E2" s="1">
@@ -15050,7 +15157,7 @@
         <v>-576</v>
       </c>
       <c r="G2" s="1">
-        <f t="shared" ref="G2:G22" si="1">E2-F2</f>
+        <f t="shared" ref="G2:G25" si="1">E2-F2</f>
         <v>-65</v>
       </c>
     </row>
@@ -15552,6 +15659,81 @@
       <c r="G22" s="22">
         <f t="shared" si="1"/>
         <v>64</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="26">
+        <v>46119</v>
+      </c>
+      <c r="B23" s="7">
+        <v>23084</v>
+      </c>
+      <c r="C23" s="7">
+        <v>17573</v>
+      </c>
+      <c r="D23" s="2">
+        <f t="shared" si="0"/>
+        <v>5511</v>
+      </c>
+      <c r="E23" s="7">
+        <v>1376</v>
+      </c>
+      <c r="F23">
+        <v>-454</v>
+      </c>
+      <c r="G23" s="22">
+        <f t="shared" si="1"/>
+        <v>1830</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="26">
+        <v>46126</v>
+      </c>
+      <c r="B24" s="7">
+        <v>18970</v>
+      </c>
+      <c r="C24" s="7">
+        <v>13800</v>
+      </c>
+      <c r="D24" s="2">
+        <f t="shared" si="0"/>
+        <v>5170</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-4114</v>
+      </c>
+      <c r="F24" s="7">
+        <v>-3773</v>
+      </c>
+      <c r="G24" s="22">
+        <f t="shared" si="1"/>
+        <v>-341</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="26">
+        <v>46133</v>
+      </c>
+      <c r="B25" s="7">
+        <v>17617</v>
+      </c>
+      <c r="C25" s="7">
+        <v>12634</v>
+      </c>
+      <c r="D25" s="2">
+        <f t="shared" si="0"/>
+        <v>4983</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-1353</v>
+      </c>
+      <c r="F25" s="7">
+        <v>-1166</v>
+      </c>
+      <c r="G25" s="22">
+        <f t="shared" si="1"/>
+        <v>-187</v>
       </c>
     </row>
   </sheetData>
@@ -15563,7 +15745,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7A64D1E-BA3D-43E2-BF69-69E226E6EEE7}">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.5703125" style="26" customWidth="1"/>
@@ -15634,7 +15816,7 @@
         <v>121577</v>
       </c>
       <c r="D3" s="11">
-        <f t="shared" ref="D3:D22" si="0">B3-C3</f>
+        <f t="shared" ref="D3:D24" si="0">B3-C3</f>
         <v>-75856</v>
       </c>
       <c r="E3" s="3">
@@ -15644,7 +15826,7 @@
         <v>-164</v>
       </c>
       <c r="G3" s="1">
-        <f t="shared" ref="G3:G22" si="1">E3-F3</f>
+        <f t="shared" ref="G3:G24" si="1">E3-F3</f>
         <v>2771</v>
       </c>
     </row>
@@ -16121,6 +16303,56 @@
       <c r="G22" s="22">
         <f t="shared" si="1"/>
         <v>7658</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="26">
+        <v>46119</v>
+      </c>
+      <c r="B23" s="7">
+        <v>137959</v>
+      </c>
+      <c r="C23" s="7">
+        <v>67146</v>
+      </c>
+      <c r="D23" s="2">
+        <f t="shared" si="0"/>
+        <v>70813</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-3816</v>
+      </c>
+      <c r="F23" s="7">
+        <v>6877</v>
+      </c>
+      <c r="G23" s="22">
+        <f t="shared" si="1"/>
+        <v>-10693</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="26">
+        <v>46133</v>
+      </c>
+      <c r="B24" s="7">
+        <v>128811</v>
+      </c>
+      <c r="C24" s="7">
+        <v>63994</v>
+      </c>
+      <c r="D24" s="2">
+        <f t="shared" si="0"/>
+        <v>64817</v>
+      </c>
+      <c r="E24">
+        <v>-706</v>
+      </c>
+      <c r="F24">
+        <v>-448</v>
+      </c>
+      <c r="G24" s="22">
+        <f t="shared" si="1"/>
+        <v>-258</v>
       </c>
     </row>
   </sheetData>
@@ -16131,7 +16363,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{484D440D-6E6B-4B12-86E6-BEF7B583A71E}">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.5703125" style="16" customWidth="1"/>
@@ -16202,7 +16434,7 @@
         <v>40931</v>
       </c>
       <c r="D3" s="11">
-        <f t="shared" ref="D3:D22" si="0">B3-C3</f>
+        <f t="shared" ref="D3:D25" si="0">B3-C3</f>
         <v>-32185</v>
       </c>
       <c r="E3" s="3">
@@ -16212,7 +16444,7 @@
         <v>-2521</v>
       </c>
       <c r="G3" s="1">
-        <f t="shared" ref="G3:G22" si="1">E3-F3</f>
+        <f t="shared" ref="G3:G25" si="1">E3-F3</f>
         <v>3864</v>
       </c>
     </row>
@@ -16689,6 +16921,81 @@
       <c r="G22" s="22">
         <f t="shared" si="1"/>
         <v>-2774</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="26">
+        <v>46119</v>
+      </c>
+      <c r="B23" s="7">
+        <v>10586</v>
+      </c>
+      <c r="C23" s="7">
+        <v>41280</v>
+      </c>
+      <c r="D23" s="28">
+        <f t="shared" si="0"/>
+        <v>-30694</v>
+      </c>
+      <c r="E23" s="7">
+        <v>1271</v>
+      </c>
+      <c r="F23" s="7">
+        <v>2094</v>
+      </c>
+      <c r="G23" s="22">
+        <f t="shared" si="1"/>
+        <v>-823</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="26">
+        <v>46126</v>
+      </c>
+      <c r="B24" s="7">
+        <v>9637</v>
+      </c>
+      <c r="C24" s="7">
+        <v>43734</v>
+      </c>
+      <c r="D24" s="28">
+        <f t="shared" si="0"/>
+        <v>-34097</v>
+      </c>
+      <c r="E24">
+        <v>-949</v>
+      </c>
+      <c r="F24" s="7">
+        <v>2454</v>
+      </c>
+      <c r="G24" s="22">
+        <f t="shared" si="1"/>
+        <v>-3403</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="26">
+        <v>46133</v>
+      </c>
+      <c r="B25" s="7">
+        <v>8372</v>
+      </c>
+      <c r="C25" s="7">
+        <v>41645</v>
+      </c>
+      <c r="D25" s="28">
+        <f t="shared" si="0"/>
+        <v>-33273</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-1265</v>
+      </c>
+      <c r="F25" s="7">
+        <v>-2089</v>
+      </c>
+      <c r="G25" s="22">
+        <f t="shared" si="1"/>
+        <v>824</v>
       </c>
     </row>
   </sheetData>
@@ -16698,7 +17005,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49E55D1F-7511-410A-9BDB-6D70A2FC177B}">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.28515625" style="16" customWidth="1"/>
@@ -16744,7 +17051,7 @@
         <v>133427</v>
       </c>
       <c r="D2" s="15">
-        <f t="shared" ref="D2:D22" si="0">B2-C2</f>
+        <f t="shared" ref="D2:D25" si="0">B2-C2</f>
         <v>-81004</v>
       </c>
       <c r="E2" s="1">
@@ -17256,6 +17563,81 @@
       <c r="G22" s="22">
         <f>E22-F22</f>
         <v>3933</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="26">
+        <v>46119</v>
+      </c>
+      <c r="B23" s="7">
+        <v>47344</v>
+      </c>
+      <c r="C23" s="7">
+        <v>103698</v>
+      </c>
+      <c r="D23" s="16">
+        <f t="shared" si="0"/>
+        <v>-56354</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-3960</v>
+      </c>
+      <c r="F23">
+        <v>-271</v>
+      </c>
+      <c r="G23" s="22">
+        <f>E23-F23</f>
+        <v>-3689</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="26">
+        <v>46126</v>
+      </c>
+      <c r="B24" s="7">
+        <v>54947</v>
+      </c>
+      <c r="C24" s="7">
+        <v>109671</v>
+      </c>
+      <c r="D24" s="16">
+        <f t="shared" si="0"/>
+        <v>-54724</v>
+      </c>
+      <c r="E24" s="7">
+        <v>7603</v>
+      </c>
+      <c r="F24" s="7">
+        <v>5973</v>
+      </c>
+      <c r="G24" s="22">
+        <f>E24-F24</f>
+        <v>1630</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="26">
+        <v>46133</v>
+      </c>
+      <c r="B25" s="7">
+        <v>63086</v>
+      </c>
+      <c r="C25" s="7">
+        <v>115125</v>
+      </c>
+      <c r="D25" s="16">
+        <f t="shared" si="0"/>
+        <v>-52039</v>
+      </c>
+      <c r="E25" s="7">
+        <v>8139</v>
+      </c>
+      <c r="F25" s="7">
+        <v>5454</v>
+      </c>
+      <c r="G25" s="22">
+        <f>E25-F25</f>
+        <v>2685</v>
       </c>
     </row>
   </sheetData>
@@ -17323,7 +17705,7 @@
         <v>4958</v>
       </c>
       <c r="G2" s="1">
-        <f t="shared" ref="G2:G22" si="1">E2-F2</f>
+        <f t="shared" ref="G2:G25" si="1">E2-F2</f>
         <v>-2789</v>
       </c>
     </row>
@@ -17828,17 +18210,80 @@
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
+      <c r="A23" s="26">
+        <v>46119</v>
+      </c>
+      <c r="B23" s="29">
+        <v>91560</v>
+      </c>
+      <c r="C23" s="29">
+        <v>185302</v>
+      </c>
+      <c r="D23" s="16">
+        <f>B23-C23</f>
+        <v>-93742</v>
+      </c>
+      <c r="E23" s="29">
+        <v>-3796</v>
+      </c>
+      <c r="F23" s="29">
+        <v>17074</v>
+      </c>
+      <c r="G23" s="2">
+        <f t="shared" si="1"/>
+        <v>-20870</v>
+      </c>
       <c r="H23" s="2"/>
     </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" s="7">
+        <v>102114</v>
+      </c>
+      <c r="C24" s="7">
+        <v>185322</v>
+      </c>
+      <c r="D24" s="16">
+        <f>B24-C24</f>
+        <v>-83208</v>
+      </c>
+      <c r="E24" s="7">
+        <v>10554</v>
+      </c>
+      <c r="F24">
+        <v>20</v>
+      </c>
+      <c r="G24" s="2">
+        <f t="shared" si="1"/>
+        <v>10534</v>
+      </c>
+    </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
+      <c r="A25" s="26">
+        <v>46133</v>
+      </c>
+      <c r="B25" s="7">
+        <v>101386</v>
+      </c>
+      <c r="C25" s="7">
+        <v>195846</v>
+      </c>
+      <c r="D25" s="16">
+        <f>B25-C25</f>
+        <v>-94460</v>
+      </c>
+      <c r="E25" s="2">
+        <v>-728</v>
+      </c>
+      <c r="F25" s="29">
+        <v>10524</v>
+      </c>
+      <c r="G25" s="2">
+        <f t="shared" si="1"/>
+        <v>-11252</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -17849,7 +18294,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FDC40EE-8D54-47CC-9557-EC14C0D36988}">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="16" customWidth="1"/>
@@ -17920,7 +18365,7 @@
         <v>173351</v>
       </c>
       <c r="D3" s="12">
-        <f t="shared" ref="D3:D22" si="0">B3-C3</f>
+        <f t="shared" ref="D3:D25" si="0">B3-C3</f>
         <v>-149099</v>
       </c>
       <c r="E3" s="3">
@@ -17930,7 +18375,7 @@
         <v>-7435</v>
       </c>
       <c r="G3" s="3">
-        <f t="shared" ref="G3:G22" si="1">E3-F3</f>
+        <f t="shared" ref="G3:G25" si="1">E3-F3</f>
         <v>8536</v>
       </c>
     </row>
@@ -18410,10 +18855,79 @@
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G23" s="7"/>
+      <c r="A23" s="26">
+        <v>46119</v>
+      </c>
+      <c r="B23" s="7">
+        <v>60714</v>
+      </c>
+      <c r="C23" s="7">
+        <v>116362</v>
+      </c>
+      <c r="D23" s="2">
+        <f t="shared" si="0"/>
+        <v>-55648</v>
+      </c>
+      <c r="E23" s="7">
+        <v>4293</v>
+      </c>
+      <c r="F23" s="7">
+        <v>27257</v>
+      </c>
+      <c r="G23" s="27">
+        <f t="shared" si="1"/>
+        <v>-22964</v>
+      </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G24" s="7"/>
+      <c r="A24" s="26">
+        <v>46126</v>
+      </c>
+      <c r="B24" s="7">
+        <v>54249</v>
+      </c>
+      <c r="C24" s="7">
+        <v>132521</v>
+      </c>
+      <c r="D24" s="2">
+        <f t="shared" si="0"/>
+        <v>-78272</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-6465</v>
+      </c>
+      <c r="F24" s="7">
+        <v>16159</v>
+      </c>
+      <c r="G24" s="27">
+        <f t="shared" si="1"/>
+        <v>-22624</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="26">
+        <v>46133</v>
+      </c>
+      <c r="B25" s="7">
+        <v>60889</v>
+      </c>
+      <c r="C25" s="7">
+        <v>119723</v>
+      </c>
+      <c r="D25" s="2">
+        <f t="shared" si="0"/>
+        <v>-58834</v>
+      </c>
+      <c r="E25" s="7">
+        <v>6640</v>
+      </c>
+      <c r="F25" s="7">
+        <v>-12798</v>
+      </c>
+      <c r="G25" s="27">
+        <f t="shared" si="1"/>
+        <v>19438</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18423,7 +18937,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71A07693-2708-497B-89D5-86A56CB2CAAA}">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -18494,7 +19008,7 @@
         <v>73468</v>
       </c>
       <c r="D3" s="7">
-        <f t="shared" ref="D3:D22" si="0">B3-C3</f>
+        <f t="shared" ref="D3:D25" si="0">B3-C3</f>
         <v>-49257</v>
       </c>
       <c r="E3" s="7">
@@ -18504,7 +19018,7 @@
         <v>722</v>
       </c>
       <c r="G3">
-        <f t="shared" ref="G3:G22" si="1">E3-F3</f>
+        <f t="shared" ref="G3:G25" si="1">E3-F3</f>
         <v>-5188</v>
       </c>
     </row>
@@ -18981,6 +19495,81 @@
       <c r="G22">
         <f t="shared" si="1"/>
         <v>-1582</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="20">
+        <v>46119</v>
+      </c>
+      <c r="B23" s="7">
+        <v>12636</v>
+      </c>
+      <c r="C23" s="7">
+        <v>48711</v>
+      </c>
+      <c r="D23" s="7">
+        <f t="shared" si="0"/>
+        <v>-36075</v>
+      </c>
+      <c r="E23" s="7">
+        <v>1973</v>
+      </c>
+      <c r="F23" s="7">
+        <v>9460</v>
+      </c>
+      <c r="G23">
+        <f t="shared" si="1"/>
+        <v>-7487</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="20">
+        <v>46126</v>
+      </c>
+      <c r="B24" s="7">
+        <v>10112</v>
+      </c>
+      <c r="C24" s="7">
+        <v>52388</v>
+      </c>
+      <c r="D24" s="7">
+        <f t="shared" si="0"/>
+        <v>-42276</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-2524</v>
+      </c>
+      <c r="F24" s="7">
+        <v>3677</v>
+      </c>
+      <c r="G24">
+        <f t="shared" si="1"/>
+        <v>-6201</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="20">
+        <v>46133</v>
+      </c>
+      <c r="B25" s="7">
+        <v>7917</v>
+      </c>
+      <c r="C25" s="7">
+        <v>56371</v>
+      </c>
+      <c r="D25" s="7">
+        <f t="shared" si="0"/>
+        <v>-48454</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-2195</v>
+      </c>
+      <c r="F25" s="7">
+        <v>3983</v>
+      </c>
+      <c r="G25">
+        <f t="shared" si="1"/>
+        <v>-6178</v>
       </c>
     </row>
   </sheetData>
